--- a/docs/downloads/diario-de-leitura-bibliotheca-latina.xlsx
+++ b/docs/downloads/diario-de-leitura-bibliotheca-latina.xlsx
@@ -722,7 +722,7 @@
     <row r="32">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Site: https://oaleffemanuel.github.io/bibliotheca-latina/  ·  Versão de 2026-10-16  ·  Licença CC BY 4.0</t>
+          <t>Site: https://oaleffemanuel.github.io/bibliotheca-latina/  ·  Versão de 2026-10-18  ·  Licença CC BY 4.0</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/diario-de-leitura-bibliotheca-latina.xlsx
+++ b/docs/downloads/diario-de-leitura-bibliotheca-latina.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summaria" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Catálogo'!$A$1:$T$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Catálogo'!$A$1:$T$146</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -811,19 +811,19 @@
         </is>
       </c>
       <c r="C6">
-        <f>COUNTIF(Catálogo!$B$2:$B$107,"I")</f>
+        <f>COUNTIF(Catálogo!$B$2:$B$146,"I")</f>
         <v/>
       </c>
       <c r="D6">
-        <f>COUNTIFS(Catálogo!$B$2:$B$107,"I",Catálogo!$P$2:$P$107,"Quero ler")</f>
+        <f>COUNTIFS(Catálogo!$B$2:$B$146,"I",Catálogo!$P$2:$P$146,"Quero ler")</f>
         <v/>
       </c>
       <c r="E6">
-        <f>COUNTIFS(Catálogo!$B$2:$B$107,"I",Catálogo!$P$2:$P$107,"Lendo")</f>
+        <f>COUNTIFS(Catálogo!$B$2:$B$146,"I",Catálogo!$P$2:$P$146,"Lendo")</f>
         <v/>
       </c>
       <c r="F6">
-        <f>COUNTIFS(Catálogo!$B$2:$B$107,"I",Catálogo!$P$2:$P$107,"Lido")</f>
+        <f>COUNTIFS(Catálogo!$B$2:$B$146,"I",Catálogo!$P$2:$P$146,"Lido")</f>
         <v/>
       </c>
       <c r="G6" s="10">
@@ -838,19 +838,19 @@
         </is>
       </c>
       <c r="C7">
-        <f>COUNTIF(Catálogo!$B$2:$B$107,"II")</f>
+        <f>COUNTIF(Catálogo!$B$2:$B$146,"II")</f>
         <v/>
       </c>
       <c r="D7">
-        <f>COUNTIFS(Catálogo!$B$2:$B$107,"II",Catálogo!$P$2:$P$107,"Quero ler")</f>
+        <f>COUNTIFS(Catálogo!$B$2:$B$146,"II",Catálogo!$P$2:$P$146,"Quero ler")</f>
         <v/>
       </c>
       <c r="E7">
-        <f>COUNTIFS(Catálogo!$B$2:$B$107,"II",Catálogo!$P$2:$P$107,"Lendo")</f>
+        <f>COUNTIFS(Catálogo!$B$2:$B$146,"II",Catálogo!$P$2:$P$146,"Lendo")</f>
         <v/>
       </c>
       <c r="F7">
-        <f>COUNTIFS(Catálogo!$B$2:$B$107,"II",Catálogo!$P$2:$P$107,"Lido")</f>
+        <f>COUNTIFS(Catálogo!$B$2:$B$146,"II",Catálogo!$P$2:$P$146,"Lido")</f>
         <v/>
       </c>
       <c r="G7" s="10">
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="C8">
-        <f>COUNTIF(Catálogo!$B$2:$B$107,"III")</f>
+        <f>COUNTIF(Catálogo!$B$2:$B$146,"III")</f>
         <v/>
       </c>
       <c r="D8">
-        <f>COUNTIFS(Catálogo!$B$2:$B$107,"III",Catálogo!$P$2:$P$107,"Quero ler")</f>
+        <f>COUNTIFS(Catálogo!$B$2:$B$146,"III",Catálogo!$P$2:$P$146,"Quero ler")</f>
         <v/>
       </c>
       <c r="E8">
-        <f>COUNTIFS(Catálogo!$B$2:$B$107,"III",Catálogo!$P$2:$P$107,"Lendo")</f>
+        <f>COUNTIFS(Catálogo!$B$2:$B$146,"III",Catálogo!$P$2:$P$146,"Lendo")</f>
         <v/>
       </c>
       <c r="F8">
-        <f>COUNTIFS(Catálogo!$B$2:$B$107,"III",Catálogo!$P$2:$P$107,"Lido")</f>
+        <f>COUNTIFS(Catálogo!$B$2:$B$146,"III",Catálogo!$P$2:$P$146,"Lido")</f>
         <v/>
       </c>
       <c r="G8" s="10">
@@ -892,19 +892,19 @@
         </is>
       </c>
       <c r="C9">
-        <f>COUNTIF(Catálogo!$B$2:$B$107,"IV")</f>
+        <f>COUNTIF(Catálogo!$B$2:$B$146,"IV")</f>
         <v/>
       </c>
       <c r="D9">
-        <f>COUNTIFS(Catálogo!$B$2:$B$107,"IV",Catálogo!$P$2:$P$107,"Quero ler")</f>
+        <f>COUNTIFS(Catálogo!$B$2:$B$146,"IV",Catálogo!$P$2:$P$146,"Quero ler")</f>
         <v/>
       </c>
       <c r="E9">
-        <f>COUNTIFS(Catálogo!$B$2:$B$107,"IV",Catálogo!$P$2:$P$107,"Lendo")</f>
+        <f>COUNTIFS(Catálogo!$B$2:$B$146,"IV",Catálogo!$P$2:$P$146,"Lendo")</f>
         <v/>
       </c>
       <c r="F9">
-        <f>COUNTIFS(Catálogo!$B$2:$B$107,"IV",Catálogo!$P$2:$P$107,"Lido")</f>
+        <f>COUNTIFS(Catálogo!$B$2:$B$146,"IV",Catálogo!$P$2:$P$146,"Lido")</f>
         <v/>
       </c>
       <c r="G9" s="10">
@@ -919,19 +919,19 @@
         </is>
       </c>
       <c r="C10">
-        <f>COUNTIF(Catálogo!$B$2:$B$107,"V")</f>
+        <f>COUNTIF(Catálogo!$B$2:$B$146,"V")</f>
         <v/>
       </c>
       <c r="D10">
-        <f>COUNTIFS(Catálogo!$B$2:$B$107,"V",Catálogo!$P$2:$P$107,"Quero ler")</f>
+        <f>COUNTIFS(Catálogo!$B$2:$B$146,"V",Catálogo!$P$2:$P$146,"Quero ler")</f>
         <v/>
       </c>
       <c r="E10">
-        <f>COUNTIFS(Catálogo!$B$2:$B$107,"V",Catálogo!$P$2:$P$107,"Lendo")</f>
+        <f>COUNTIFS(Catálogo!$B$2:$B$146,"V",Catálogo!$P$2:$P$146,"Lendo")</f>
         <v/>
       </c>
       <c r="F10">
-        <f>COUNTIFS(Catálogo!$B$2:$B$107,"V",Catálogo!$P$2:$P$107,"Lido")</f>
+        <f>COUNTIFS(Catálogo!$B$2:$B$146,"V",Catálogo!$P$2:$P$146,"Lido")</f>
         <v/>
       </c>
       <c r="G10" s="10">
@@ -946,19 +946,19 @@
         </is>
       </c>
       <c r="C11">
-        <f>COUNTIF(Catálogo!$B$2:$B$107,"VI")</f>
+        <f>COUNTIF(Catálogo!$B$2:$B$146,"VI")</f>
         <v/>
       </c>
       <c r="D11">
-        <f>COUNTIFS(Catálogo!$B$2:$B$107,"VI",Catálogo!$P$2:$P$107,"Quero ler")</f>
+        <f>COUNTIFS(Catálogo!$B$2:$B$146,"VI",Catálogo!$P$2:$P$146,"Quero ler")</f>
         <v/>
       </c>
       <c r="E11">
-        <f>COUNTIFS(Catálogo!$B$2:$B$107,"VI",Catálogo!$P$2:$P$107,"Lendo")</f>
+        <f>COUNTIFS(Catálogo!$B$2:$B$146,"VI",Catálogo!$P$2:$P$146,"Lendo")</f>
         <v/>
       </c>
       <c r="F11">
-        <f>COUNTIFS(Catálogo!$B$2:$B$107,"VI",Catálogo!$P$2:$P$107,"Lido")</f>
+        <f>COUNTIFS(Catálogo!$B$2:$B$146,"VI",Catálogo!$P$2:$P$146,"Lido")</f>
         <v/>
       </c>
       <c r="G11" s="10">
@@ -973,19 +973,19 @@
         </is>
       </c>
       <c r="C12">
-        <f>COUNTIF(Catálogo!$B$2:$B$107,"VII")</f>
+        <f>COUNTIF(Catálogo!$B$2:$B$146,"VII")</f>
         <v/>
       </c>
       <c r="D12">
-        <f>COUNTIFS(Catálogo!$B$2:$B$107,"VII",Catálogo!$P$2:$P$107,"Quero ler")</f>
+        <f>COUNTIFS(Catálogo!$B$2:$B$146,"VII",Catálogo!$P$2:$P$146,"Quero ler")</f>
         <v/>
       </c>
       <c r="E12">
-        <f>COUNTIFS(Catálogo!$B$2:$B$107,"VII",Catálogo!$P$2:$P$107,"Lendo")</f>
+        <f>COUNTIFS(Catálogo!$B$2:$B$146,"VII",Catálogo!$P$2:$P$146,"Lendo")</f>
         <v/>
       </c>
       <c r="F12">
-        <f>COUNTIFS(Catálogo!$B$2:$B$107,"VII",Catálogo!$P$2:$P$107,"Lido")</f>
+        <f>COUNTIFS(Catálogo!$B$2:$B$146,"VII",Catálogo!$P$2:$P$146,"Lido")</f>
         <v/>
       </c>
       <c r="G12" s="10">
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T107"/>
+  <dimension ref="A1:T146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4377,12 +4377,12 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Selections from Erasmus, principally from his Epistles</t>
+          <t>Commentarii de bello civili (texto integral)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Desiderius Erasmus (ed. P. S. Allen)</t>
+          <t>Gaius Iulius Caesar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4400,17 +4400,17 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>Renascentista e neolatino</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>Epistolografia</t>
+          <t>Historiografia</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>Project Gutenberg</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4421,7 +4421,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, EPUB, Texto</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O45" s="13" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Colloquia familiaria</t>
+          <t>Selections from Erasmus, principally from his Epistles</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Desiderius Erasmus Roterodamus</t>
+          <t>Desiderius Erasmus (ed. P. S. Allen)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4478,12 +4478,12 @@
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>Diálogo</t>
+          <t>Epistolografia</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>Vicifons (Latin Wikisource)</t>
+          <t>Project Gutenberg</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4494,7 +4494,7 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, EPUB, PDF</t>
+          <t>Leitura online, EPUB, Texto</t>
         </is>
       </c>
       <c r="O46" s="13" t="inlineStr">
@@ -4523,38 +4523,40 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Gildersleeve's Latin Grammar</t>
+          <t>Colloquia familiaria</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Basil L. Gildersleeve e Gonzalez Lodge</t>
+          <t>Desiderius Erasmus Roterodamus</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gramática e referência</t>
+          <t>Leitura</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Didático</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>3</v>
+      </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>Moderno (material didático)</t>
+          <t>Renascentista e neolatino</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>Gramática</t>
+          <t>Diálogo</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>Internet Archive</t>
+          <t>Vicifons (Latin Wikisource)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4565,7 +4567,7 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>PDF, Leitura online</t>
+          <t>Leitura online, EPUB, PDF</t>
         </is>
       </c>
       <c r="O47" s="13" t="inlineStr">
@@ -4594,17 +4596,17 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>The Latin Library</t>
+          <t>Facta et dicta memorabilia</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>William L. Carey (mantenedor)</t>
+          <t>Valerius Maximus</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ferramenta</t>
+          <t>Leitura</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4612,20 +4614,22 @@
           <t>Original</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
+      <c r="H48" t="n">
+        <v>3</v>
+      </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>Moderno (material didático)</t>
+          <t>Pós-clássico</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>Ferramenta</t>
+          <t>Historiografia</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>The Latin Library</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4636,7 +4640,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>Leitura online</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O48" s="13" t="inlineStr">
@@ -4665,17 +4669,17 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Vicipaedia</t>
+          <t>Epitome rerum Romanarum</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Comunidade Vicipaedia</t>
+          <t>Lucius Annaeus Florus</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ferramenta</t>
+          <t>Leitura</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4688,17 +4692,17 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>Moderno (material didático)</t>
+          <t>Pós-clássico</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>Enciclopédia</t>
+          <t>Historiografia</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>Vicipaedia</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4709,7 +4713,7 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>Leitura online</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O49" s="13" t="inlineStr">
@@ -4728,50 +4732,48 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Auctores Romani</t>
+          <t>Ad Fontes</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>De Imperio Cn. Pompei, 27–49</t>
+          <t>Gildersleeve's Latin Grammar</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Marcus Tullius Cicero</t>
+          <t>Basil L. Gildersleeve e Gonzalez Lodge</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Leitura</t>
+          <t>Gramática e referência</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Original</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>4</v>
-      </c>
+          <t>Didático</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>Clássico</t>
+          <t>Moderno (material didático)</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>Oratória</t>
+          <t>Gramática</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>Dickinson College Commentaries</t>
+          <t>Internet Archive</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4779,14 +4781,10 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, PDF, Impresso, Áudio</t>
+          <t>PDF, Leitura online</t>
         </is>
       </c>
       <c r="O50" s="13" t="inlineStr">
@@ -4805,27 +4803,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Auctores Romani</t>
+          <t>Ad Fontes</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>In Catilinam I, com notas e vocabulário</t>
+          <t>The Latin Library</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Marcus Tullius Cicero (ed. John Henderson)</t>
+          <t>William L. Carey (mantenedor)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Leitura</t>
+          <t>Ferramenta</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4833,22 +4831,20 @@
           <t>Original</t>
         </is>
       </c>
-      <c r="H51" t="n">
-        <v>4</v>
-      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>Clássico</t>
+          <t>Moderno (material didático)</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>Oratória</t>
+          <t>Ferramenta</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>Project Gutenberg</t>
+          <t>The Latin Library</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4859,7 +4855,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, EPUB, Texto</t>
+          <t>Leitura online</t>
         </is>
       </c>
       <c r="O51" s="13" t="inlineStr">
@@ -4878,27 +4874,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Auctores Romani</t>
+          <t>Ad Fontes</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>In Catilinam I–IV</t>
+          <t>Vicipaedia</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Marcus Tullius Cicero</t>
+          <t>Comunidade Vicipaedia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Leitura</t>
+          <t>Ferramenta</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4907,21 +4903,21 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>Clássico</t>
+          <t>Moderno (material didático)</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>Oratória</t>
+          <t>Enciclopédia</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>Perseus Digital Library</t>
+          <t>Vicipaedia</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4932,7 +4928,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, EPUB</t>
+          <t>Leitura online</t>
         </is>
       </c>
       <c r="O52" s="13" t="inlineStr">
@@ -4961,12 +4957,12 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Epistulae (33 cartas selecionadas)</t>
+          <t>De Imperio Cn. Pompei, 27–49</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gaius Plinius Caecilius Secundus</t>
+          <t>Marcus Tullius Cicero</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4980,16 +4976,16 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>Pós-clássico</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>Epistolografia</t>
+          <t>Oratória</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
@@ -5002,10 +4998,14 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>Leitura online</t>
+          <t>Leitura online, PDF, Impresso, Áudio</t>
         </is>
       </c>
       <c r="O53" s="13" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Laelius de Amicitia</t>
+          <t>In Catilinam I, com notas e vocabulário</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Marcus Tullius Cicero</t>
+          <t>Marcus Tullius Cicero (ed. John Henderson)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5062,12 +5062,12 @@
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>Filosofia</t>
+          <t>Oratória</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>Perseus Digital Library</t>
+          <t>Project Gutenberg</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5078,7 +5078,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>Leitura online</t>
+          <t>Leitura online, EPUB, Texto</t>
         </is>
       </c>
       <c r="O54" s="13" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Cato Maior de Senectute</t>
+          <t>Pro Archia poeta</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>Filosofia</t>
+          <t>Oratória</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
@@ -5151,7 +5151,7 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, EPUB</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O55" s="13" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>De Officiis (latim e inglês)</t>
+          <t>Commentariolum petitionis</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Marcus Tullius Cicero</t>
+          <t>Quintus Tullius Cicero</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>Filosofia</t>
+          <t>Epistolografia</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>Project Gutenberg</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5224,7 +5224,7 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, EPUB, Texto</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O56" s="13" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Epistulae Morales ad Lucilium</t>
+          <t>In Catilinam I–IV</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Lucius Annaeus Seneca</t>
+          <t>Marcus Tullius Cicero</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5272,16 +5272,16 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>Pós-clássico</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>Filosofia</t>
+          <t>Oratória</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
@@ -5294,14 +5294,10 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, Áudio</t>
+          <t>Leitura online, EPUB</t>
         </is>
       </c>
       <c r="O57" s="13" t="inlineStr">
@@ -5330,12 +5326,12 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Somnium Scipionis (De re publica VI)</t>
+          <t>Epistulae (33 cartas selecionadas)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Marcus Tullius Cicero</t>
+          <t>Gaius Plinius Caecilius Secundus</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5349,21 +5345,21 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>Clássico</t>
+          <t>Pós-clássico</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>Filosofia</t>
+          <t>Epistolografia</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>Vicifons (Latin Wikisource)</t>
+          <t>Dickinson College Commentaries</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5374,7 +5370,7 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, EPUB, PDF</t>
+          <t>Leitura online</t>
         </is>
       </c>
       <c r="O58" s="13" t="inlineStr">
@@ -5403,12 +5399,12 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Bellum Catilinae</t>
+          <t>Laelius de Amicitia</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Gaius Sallustius Crispus</t>
+          <t>Marcus Tullius Cicero</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5431,7 +5427,7 @@
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>Historiografia</t>
+          <t>Filosofia</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
@@ -5447,7 +5443,7 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, EPUB</t>
+          <t>Leitura online</t>
         </is>
       </c>
       <c r="O59" s="13" t="inlineStr">
@@ -5476,12 +5472,12 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Ab urbe condita, liber I</t>
+          <t>Cato Maior de Senectute</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Titus Livius</t>
+          <t>Marcus Tullius Cicero</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5504,7 +5500,7 @@
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>Historiografia</t>
+          <t>Filosofia</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
@@ -5520,7 +5516,7 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>Leitura online</t>
+          <t>Leitura online, EPUB</t>
         </is>
       </c>
       <c r="O60" s="13" t="inlineStr">
@@ -5549,12 +5545,12 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Amores, liber I</t>
+          <t>De Officiis (latim e inglês)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Publius Ovidius Naso</t>
+          <t>Marcus Tullius Cicero</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5577,12 +5573,12 @@
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>Poesia elegíaca</t>
+          <t>Filosofia</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>Dickinson College Commentaries</t>
+          <t>Project Gutenberg</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5590,14 +5586,10 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, PDF, Impresso, Áudio</t>
+          <t>Leitura online, EPUB, Texto</t>
         </is>
       </c>
       <c r="O61" s="13" t="inlineStr">
@@ -5626,12 +5618,12 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Catulli Carmina</t>
+          <t>De natura deorum</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Gaius Valerius Catullus</t>
+          <t>Marcus Tullius Cicero</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5645,7 +5637,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
@@ -5654,12 +5646,12 @@
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>Poesia lírica</t>
+          <t>Filosofia</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>Project Gutenberg</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5667,14 +5659,10 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, EPUB, Texto, Áudio</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O62" s="13" t="inlineStr">
@@ -5703,12 +5691,12 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Metamorphoses III, 511–733 (Penteu)</t>
+          <t>De finibus bonorum et malorum</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Publius Ovidius Naso</t>
+          <t>Marcus Tullius Cicero</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5722,7 +5710,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
@@ -5731,12 +5719,12 @@
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>Poesia épica</t>
+          <t>Filosofia</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>Open Book Publishers</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5747,7 +5735,7 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, PDF, EPUB, Impresso</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O63" s="13" t="inlineStr">
@@ -5776,12 +5764,12 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Metamorphoses (texto integral)</t>
+          <t>Epistulae Morales ad Lucilium</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Publius Ovidius Naso</t>
+          <t>Lucius Annaeus Seneca</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5795,16 +5783,16 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>Clássico</t>
+          <t>Pós-clássico</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>Poesia épica</t>
+          <t>Filosofia</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
@@ -5817,10 +5805,14 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>Leitura online</t>
+          <t>Leitura online, Áudio</t>
         </is>
       </c>
       <c r="O64" s="13" t="inlineStr">
@@ -5849,12 +5841,12 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Aeneis (seleções)</t>
+          <t>Apocolocyntosis</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Publius Vergilius Maro</t>
+          <t>Lucius Annaeus Seneca</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5872,17 +5864,17 @@
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>Clássico</t>
+          <t>Pós-clássico</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>Poesia épica</t>
+          <t>Sátira</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>Dickinson College Commentaries</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5890,14 +5882,10 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, Áudio</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O65" s="13" t="inlineStr">
@@ -5926,12 +5914,12 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Aeneis (texto integral)</t>
+          <t>Somnium Scipionis (De re publica VI)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Publius Vergilius Maro</t>
+          <t>Marcus Tullius Cicero</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5945,7 +5933,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
@@ -5954,12 +5942,12 @@
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>Poesia épica</t>
+          <t>Filosofia</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>Perseus Digital Library</t>
+          <t>Vicifons (Latin Wikisource)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5967,14 +5955,10 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, EPUB, Áudio</t>
+          <t>Leitura online, EPUB, PDF</t>
         </is>
       </c>
       <c r="O66" s="13" t="inlineStr">
@@ -6003,12 +5987,12 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Bucolica (Eclogae)</t>
+          <t>Bellum Catilinae</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Publius Vergilius Maro</t>
+          <t>Gaius Sallustius Crispus</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -6031,12 +6015,12 @@
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>Poesia bucólica</t>
+          <t>Historiografia</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>Project Gutenberg</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6044,14 +6028,10 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, EPUB, Texto, Áudio</t>
+          <t>Leitura online, EPUB</t>
         </is>
       </c>
       <c r="O67" s="13" t="inlineStr">
@@ -6080,12 +6060,12 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Aeneis IV, 1–299 (Dido)</t>
+          <t>Bellum Iugurthinum</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Publius Vergilius Maro</t>
+          <t>Gaius Sallustius Crispus</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -6108,12 +6088,12 @@
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>Poesia épica</t>
+          <t>Historiografia</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>Open Book Publishers</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6124,7 +6104,7 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, PDF, EPUB, Impresso</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O68" s="13" t="inlineStr">
@@ -6153,12 +6133,12 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Aeneis XI (Palante e Camila), seleções</t>
+          <t>Ab urbe condita, liber I</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Publius Vergilius Maro</t>
+          <t>Titus Livius</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -6181,12 +6161,12 @@
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>Poesia épica</t>
+          <t>Historiografia</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>Open Book Publishers</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6197,7 +6177,7 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, PDF, EPUB, Impresso</t>
+          <t>Leitura online</t>
         </is>
       </c>
       <c r="O69" s="13" t="inlineStr">
@@ -6226,12 +6206,12 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>In Verrem II.1, 53–86</t>
+          <t>Amores, liber I</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Marcus Tullius Cicero</t>
+          <t>Publius Ovidius Naso</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -6254,7 +6234,7 @@
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>Oratória</t>
+          <t>Poesia elegíaca</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
@@ -6303,12 +6283,12 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Philippica II (seleções)</t>
+          <t>Catulli Carmina</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Marcus Tullius Cicero</t>
+          <t>Gaius Valerius Catullus</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6322,7 +6302,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
@@ -6331,12 +6311,12 @@
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>Oratória</t>
+          <t>Poesia lírica</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>Dickinson College Commentaries</t>
+          <t>Project Gutenberg</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -6344,10 +6324,14 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, PDF, Impresso</t>
+          <t>Leitura online, EPUB, Texto, Áudio</t>
         </is>
       </c>
       <c r="O71" s="13" t="inlineStr">
@@ -6376,12 +6360,12 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Agricola</t>
+          <t>Elegiae</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Publius Cornelius Tacitus</t>
+          <t>Albius Tibullus</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -6399,17 +6383,17 @@
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>Pós-clássico</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>Biografia</t>
+          <t>Poesia elegíaca</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>Dickinson College Commentaries</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -6417,14 +6401,10 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, Áudio</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O72" s="13" t="inlineStr">
@@ -6453,12 +6433,12 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Annales XV, 20–23 e 33–45</t>
+          <t>Metamorphoses III, 511–733 (Penteu)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Publius Cornelius Tacitus</t>
+          <t>Publius Ovidius Naso</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -6472,21 +6452,21 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>Pós-clássico</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>Historiografia</t>
+          <t>Poesia épica</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>Dickinson College Commentaries</t>
+          <t>Open Book Publishers</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -6494,14 +6474,10 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
+      <c r="M73" t="inlineStr"/>
       <c r="N73" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, PDF, Impresso, Áudio</t>
+          <t>Leitura online, PDF, EPUB, Impresso</t>
         </is>
       </c>
       <c r="O73" s="13" t="inlineStr">
@@ -6530,12 +6506,12 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Carmina et Epodi (Odes e Epodos)</t>
+          <t>Heroides (Epistulae heroidum)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Quintus Horatius Flaccus</t>
+          <t>Publius Ovidius Naso</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -6549,7 +6525,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
@@ -6558,12 +6534,12 @@
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>Poesia lírica</t>
+          <t>Poesia elegíaca</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>Project Gutenberg</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6574,7 +6550,7 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, EPUB, Texto</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O74" s="13" t="inlineStr">
@@ -6603,12 +6579,12 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Georgica, liber IV</t>
+          <t>Metamorphoses (texto integral)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Publius Vergilius Maro</t>
+          <t>Publius Ovidius Naso</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -6622,7 +6598,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
@@ -6631,12 +6607,12 @@
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>Poesia didática</t>
+          <t>Poesia épica</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>Dickinson College Commentaries</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6644,14 +6620,10 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, Áudio</t>
+          <t>Leitura online</t>
         </is>
       </c>
       <c r="O75" s="13" t="inlineStr">
@@ -6680,12 +6652,12 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Apologia (Pro se de magia)</t>
+          <t>Aeneis (seleções)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Apuleius Madaurensis</t>
+          <t>Publius Vergilius Maro</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6699,16 +6671,16 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>Pós-clássico</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>Oratória</t>
+          <t>Poesia épica</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
@@ -6721,10 +6693,14 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>Leitura online</t>
+          <t>Leitura online, Áudio</t>
         </is>
       </c>
       <c r="O76" s="13" t="inlineStr">
@@ -6743,22 +6719,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Latinitas Christiana</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Biblia Sacra Vulgata (editio Clementina)</t>
+          <t>Aeneis (texto integral)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hieronymus Stridonensis (Vulgata)</t>
+          <t>Publius Vergilius Maro</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -6772,21 +6748,21 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>Tardio e patrístico</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>Escritura (Vulgata)</t>
+          <t>Poesia épica</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>Vicifons (Latin Wikisource)</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6801,7 +6777,7 @@
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, EPUB, PDF, Áudio</t>
+          <t>Leitura online, EPUB, Áudio</t>
         </is>
       </c>
       <c r="O77" s="13" t="inlineStr">
@@ -6820,22 +6796,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Latinitas Christiana</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Prophetia Ionae (Vulgata)</t>
+          <t>Pharsalia (Bellum civile)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hieronymus Stridonensis (Vulgata)</t>
+          <t>Marcus Annaeus Lucanus</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -6849,21 +6825,21 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>Tardio e patrístico</t>
+          <t>Pós-clássico</t>
         </is>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>Escritura (Vulgata)</t>
+          <t>Poesia épica</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>Project Gutenberg</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6874,7 +6850,7 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, EPUB, Texto</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O78" s="13" t="inlineStr">
@@ -6893,22 +6869,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Latinitas Christiana</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Regula sancti Benedicti</t>
+          <t>Bucolica (Eclogae)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Benedictus Nursinus</t>
+          <t>Publius Vergilius Maro</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -6922,21 +6898,21 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>Tardio e patrístico</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>Regra monástica</t>
+          <t>Poesia bucólica</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>Vicifons (Latin Wikisource)</t>
+          <t>Project Gutenberg</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6951,7 +6927,7 @@
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, EPUB, PDF, Áudio</t>
+          <t>Leitura online, EPUB, Texto, Áudio</t>
         </is>
       </c>
       <c r="O79" s="13" t="inlineStr">
@@ -6970,22 +6946,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Latinitas Christiana</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Vita Sancti Martini</t>
+          <t>Aeneis IV, 1–299 (Dido)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sulpicius Severus</t>
+          <t>Publius Vergilius Maro</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -6999,21 +6975,21 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>Tardio e patrístico</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>Hagiografia</t>
+          <t>Poesia épica</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>Dickinson College Commentaries</t>
+          <t>Open Book Publishers</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -7021,14 +6997,10 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
+      <c r="M80" t="inlineStr"/>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, Áudio</t>
+          <t>Leitura online, PDF, EPUB, Impresso</t>
         </is>
       </c>
       <c r="O80" s="13" t="inlineStr">
@@ -7047,22 +7019,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Latinitas Christiana</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>De imitatione Christi</t>
+          <t>Comoediae (as seis comédias)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Thomas a Kempis</t>
+          <t>Publius Terentius Afer</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -7076,21 +7048,21 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>Medieval</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>Espiritualidade</t>
+          <t>Comédia</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>Vicifons (Latin Wikisource)</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -7098,14 +7070,10 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, EPUB, PDF, Áudio</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O81" s="13" t="inlineStr">
@@ -7124,22 +7092,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Latinitas Christiana</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Vita Malchi monachi captivi</t>
+          <t>Amphitruo</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Hieronymus Stridonensis</t>
+          <t>Titus Maccius Plautus</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -7153,21 +7121,21 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>Tardio e patrístico</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>Hagiografia</t>
+          <t>Comédia</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>Dickinson College Commentaries</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -7178,7 +7146,7 @@
       <c r="M82" t="inlineStr"/>
       <c r="N82" s="4" t="inlineStr">
         <is>
-          <t>Leitura online</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O82" s="13" t="inlineStr">
@@ -7197,22 +7165,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Latinitas Christiana</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Vita Sancti Pauli primi eremitae</t>
+          <t>Aulularia</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hieronymus Stridonensis</t>
+          <t>Titus Maccius Plautus</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -7226,21 +7194,21 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>Tardio e patrístico</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>Hagiografia</t>
+          <t>Comédia</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>Corpus Corporum</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -7270,22 +7238,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Latinitas Christiana</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Confessiones</t>
+          <t>Captivi</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Augustinus Hipponensis</t>
+          <t>Titus Maccius Plautus</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -7299,21 +7267,21 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
-          <t>Tardio e patrístico</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>Autobiografia</t>
+          <t>Comédia</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>Corpus Corporum</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -7321,14 +7289,10 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
+      <c r="M84" t="inlineStr"/>
       <c r="N84" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, XML, EPUB, Áudio</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O84" s="13" t="inlineStr">
@@ -7347,22 +7311,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Latinitas Christiana</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Epistulae (18 cartas selecionadas)</t>
+          <t>Menaechmi</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hieronymus Stridonensis</t>
+          <t>Titus Maccius Plautus</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -7376,16 +7340,16 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>Tardio e patrístico</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>Epistolografia</t>
+          <t>Comédia</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
@@ -7401,7 +7365,7 @@
       <c r="M85" t="inlineStr"/>
       <c r="N85" s="4" t="inlineStr">
         <is>
-          <t>Leitura online</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O85" s="13" t="inlineStr">
@@ -7420,22 +7384,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Latinitas Christiana</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Epistolae (texto integral)</t>
+          <t>Miles gloriosus</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Hieronymus Stridonensis</t>
+          <t>Titus Maccius Plautus</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -7449,21 +7413,21 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I86" s="4" t="inlineStr">
         <is>
-          <t>Tardio e patrístico</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>Epistolografia</t>
+          <t>Comédia</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>Corpus Corporum</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -7493,22 +7457,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Latinitas Christiana</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Epistulae (cartas selecionadas)</t>
+          <t>Mostellaria</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Augustinus Hipponensis</t>
+          <t>Titus Maccius Plautus</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -7522,16 +7486,16 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>Tardio e patrístico</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>Epistolografia</t>
+          <t>Comédia</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
@@ -7547,7 +7511,7 @@
       <c r="M87" t="inlineStr"/>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t>Leitura online</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O87" s="13" t="inlineStr">
@@ -7566,22 +7530,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Latinitas Christiana</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>De civitate Dei</t>
+          <t>Aeneis XI (Palante e Camila), seleções</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Augustinus Hipponensis</t>
+          <t>Publius Vergilius Maro</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -7599,17 +7563,17 @@
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t>Tardio e patrístico</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>Teologia</t>
+          <t>Poesia épica</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>Corpus Corporum</t>
+          <t>Open Book Publishers</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7617,14 +7581,10 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
+      <c r="M88" t="inlineStr"/>
       <c r="N88" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, XML, Áudio</t>
+          <t>Leitura online, PDF, EPUB, Impresso</t>
         </is>
       </c>
       <c r="O88" s="13" t="inlineStr">
@@ -7643,22 +7603,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Latinitas Christiana</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Te Deum</t>
+          <t>In Verrem II.1, 53–86</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Atribuído a Nicetas de Remesiana ou a Ambrósio</t>
+          <t>Marcus Tullius Cicero</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -7672,21 +7632,21 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>Tardio e patrístico</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>Hino</t>
+          <t>Oratória</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>Vicifons (Latin Wikisource)</t>
+          <t>Dickinson College Commentaries</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -7694,10 +7654,14 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="N89" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, EPUB, PDF</t>
+          <t>Leitura online, PDF, Impresso, Áudio</t>
         </is>
       </c>
       <c r="O89" s="13" t="inlineStr">
@@ -7716,22 +7680,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Latinitas Christiana</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Pange lingua gloriosi corporis mysterium</t>
+          <t>Pro Caelio</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Thomas de Aquino</t>
+          <t>Marcus Tullius Cicero</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -7745,21 +7709,21 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>Medieval</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>Hino</t>
+          <t>Oratória</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>Vicifons (Latin Wikisource)</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -7770,7 +7734,7 @@
       <c r="M90" t="inlineStr"/>
       <c r="N90" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, EPUB, PDF</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O90" s="13" t="inlineStr">
@@ -7789,22 +7753,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Latinitas Christiana</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Dies irae</t>
+          <t>Pro Milone</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Atribuído a Thomas de Celano</t>
+          <t>Marcus Tullius Cicero</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -7818,21 +7782,21 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>Medieval</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>Hino</t>
+          <t>Oratória</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>Vicifons (Latin Wikisource)</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -7843,7 +7807,7 @@
       <c r="M91" t="inlineStr"/>
       <c r="N91" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, EPUB, PDF</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O91" s="13" t="inlineStr">
@@ -7862,22 +7826,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Latinitas Christiana</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Stabat Mater</t>
+          <t>Philippica II (seleções)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Atribuído a Jacopone da Todi</t>
+          <t>Marcus Tullius Cicero</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -7891,21 +7855,21 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>Medieval</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>Hino</t>
+          <t>Oratória</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>Vicifons (Latin Wikisource)</t>
+          <t>Dickinson College Commentaries</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -7913,14 +7877,10 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
+      <c r="M92" t="inlineStr"/>
       <c r="N92" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, EPUB, PDF, Áudio</t>
+          <t>Leitura online, PDF, Impresso</t>
         </is>
       </c>
       <c r="O92" s="13" t="inlineStr">
@@ -7939,22 +7899,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VII</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sapientia Mediaevalis</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Navigatio Sancti Brendani Abbatis</t>
+          <t>Philippicae I–XIV (texto integral)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Anônimo (séc. IX–X)</t>
+          <t>Marcus Tullius Cicero</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -7968,21 +7928,21 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>Medieval</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>Narrativa</t>
+          <t>Oratória</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>Dickinson College Commentaries</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7993,7 +7953,7 @@
       <c r="M93" t="inlineStr"/>
       <c r="N93" s="4" t="inlineStr">
         <is>
-          <t>Leitura online</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O93" s="13" t="inlineStr">
@@ -8012,22 +7972,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>VII</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sapientia Mediaevalis</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Gesta Romanorum (edição Oesterley)</t>
+          <t>De oratore</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Anônimo (séc. XIII–XIV)</t>
+          <t>Marcus Tullius Cicero</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -8041,21 +8001,21 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>Medieval</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>Narrativa</t>
+          <t>Retórica</t>
         </is>
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>Vicifons (Latin Wikisource)</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -8066,7 +8026,7 @@
       <c r="M94" t="inlineStr"/>
       <c r="N94" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, EPUB, PDF</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O94" s="13" t="inlineStr">
@@ -8085,22 +8045,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>VII</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sapientia Mediaevalis</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>De consolatione philosophiae</t>
+          <t>Epistulae ad familiares</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Anicius Manlius Severinus Boethius</t>
+          <t>Marcus Tullius Cicero</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -8118,17 +8078,17 @@
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>Tardio e patrístico</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>Filosofia</t>
+          <t>Epistolografia</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>Corpus Corporum</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -8136,14 +8096,10 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
+      <c r="M95" t="inlineStr"/>
       <c r="N95" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, XML, EPUB, Áudio</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O95" s="13" t="inlineStr">
@@ -8162,22 +8118,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>VII</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sapientia Mediaevalis</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Historia Ecclesiastica gentis Anglorum (seleções)</t>
+          <t>Epistulae ad Atticum</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Beda Venerabilis</t>
+          <t>Marcus Tullius Cicero</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -8191,21 +8147,21 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>Medieval</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>Historiografia</t>
+          <t>Epistolografia</t>
         </is>
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>Dickinson College Commentaries</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -8216,7 +8172,7 @@
       <c r="M96" t="inlineStr"/>
       <c r="N96" s="4" t="inlineStr">
         <is>
-          <t>Leitura online</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O96" s="13" t="inlineStr">
@@ -8235,22 +8191,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>VII</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sapientia Mediaevalis</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Vita Karoli Magni</t>
+          <t>De vita Caesarum (as doze vidas)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Einhardus</t>
+          <t>Gaius Suetonius Tranquillus</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -8268,7 +8224,7 @@
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>Medieval</t>
+          <t>Pós-clássico</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
@@ -8278,7 +8234,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>Vicifons (Latin Wikisource)</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -8289,7 +8245,7 @@
       <c r="M97" t="inlineStr"/>
       <c r="N97" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, EPUB, PDF</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O97" s="13" t="inlineStr">
@@ -8308,22 +8264,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>VII</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sapientia Mediaevalis</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Gesta Francorum et aliorum Hierosolimitanorum</t>
+          <t>Satyricon</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Anônimo (c. 1100)</t>
+          <t>Gaius Petronius Arbiter</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -8337,21 +8293,21 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>Medieval</t>
+          <t>Pós-clássico</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>Historiografia</t>
+          <t>Romance</t>
         </is>
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>Dickinson College Commentaries</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -8362,7 +8318,7 @@
       <c r="M98" t="inlineStr"/>
       <c r="N98" s="4" t="inlineStr">
         <is>
-          <t>Leitura online</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O98" s="13" t="inlineStr">
@@ -8381,22 +8337,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>VII</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Sapientia Mediaevalis</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Legenda aurea (capítulos transcritos)</t>
+          <t>Noctes Atticae</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Iacobus de Voragine</t>
+          <t>Aulus Gellius</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -8410,21 +8366,21 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>Medieval</t>
+          <t>Pós-clássico</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>Hagiografia</t>
+          <t>Miscelânea</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>Vicifons (Latin Wikisource)</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -8435,7 +8391,7 @@
       <c r="M99" t="inlineStr"/>
       <c r="N99" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, EPUB, PDF</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O99" s="13" t="inlineStr">
@@ -8454,22 +8410,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>VII</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sapientia Mediaevalis</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Proslogion</t>
+          <t>Historiae Alexandri Magni</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Anselmus Cantuariensis</t>
+          <t>Quintus Curtius Rufus</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -8483,21 +8439,21 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>Medieval</t>
+          <t>Pós-clássico</t>
         </is>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>Filosofia</t>
+          <t>Historiografia</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>Corpus Corporum</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -8527,22 +8483,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>VII</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sapientia Mediaevalis</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Etymologiae</t>
+          <t>Agricola</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Isidorus Hispalensis</t>
+          <t>Publius Cornelius Tacitus</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -8556,21 +8512,21 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>Medieval</t>
+          <t>Pós-clássico</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>Enciclopédia</t>
+          <t>Biografia</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>Corpus Corporum</t>
+          <t>Dickinson College Commentaries</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -8578,10 +8534,14 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="N101" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, XML</t>
+          <t>Leitura online, Áudio</t>
         </is>
       </c>
       <c r="O101" s="13" t="inlineStr">
@@ -8600,22 +8560,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>VII</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sapientia Mediaevalis</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>De diligendo Deo</t>
+          <t>Germania</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bernardus Claraevallensis</t>
+          <t>Publius Cornelius Tacitus</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -8629,21 +8589,21 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
-          <t>Medieval</t>
+          <t>Pós-clássico</t>
         </is>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>Teologia</t>
+          <t>Etnografia</t>
         </is>
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>Corpus Corporum</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -8673,22 +8633,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>VII</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Sapientia Mediaevalis</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Didascalicon (Eruditio didascalica)</t>
+          <t>Annales XV, 20–23 e 33–45</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hugo de Sancto Victore</t>
+          <t>Publius Cornelius Tacitus</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -8702,21 +8662,21 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>Medieval</t>
+          <t>Pós-clássico</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>Filosofia</t>
+          <t>Historiografia</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>Corpus Corporum</t>
+          <t>Dickinson College Commentaries</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -8724,10 +8684,14 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="N103" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, XML</t>
+          <t>Leitura online, PDF, Impresso, Áudio</t>
         </is>
       </c>
       <c r="O103" s="13" t="inlineStr">
@@ -8746,22 +8710,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>VII</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Sapientia Mediaevalis</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Summa Theologiae, Prima pars</t>
+          <t>Annales (texto integral)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Thomas de Aquino</t>
+          <t>Publius Cornelius Tacitus</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -8775,21 +8739,21 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>Medieval</t>
+          <t>Pós-clássico</t>
         </is>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>Teologia</t>
+          <t>Historiografia</t>
         </is>
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>Corpus Thomisticum</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -8800,7 +8764,7 @@
       <c r="M104" t="inlineStr"/>
       <c r="N104" s="4" t="inlineStr">
         <is>
-          <t>Leitura online</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O104" s="13" t="inlineStr">
@@ -8819,22 +8783,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>VII</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Sapientia Mediaevalis</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>De ente et essentia</t>
+          <t>Carmina et Epodi (Odes e Epodos)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Thomas de Aquino</t>
+          <t>Quintus Horatius Flaccus</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -8848,21 +8812,21 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>Medieval</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>Filosofia</t>
+          <t>Poesia lírica</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>Corpus Thomisticum</t>
+          <t>Project Gutenberg</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -8873,7 +8837,7 @@
       <c r="M105" t="inlineStr"/>
       <c r="N105" s="4" t="inlineStr">
         <is>
-          <t>Leitura online</t>
+          <t>Leitura online, EPUB, Texto</t>
         </is>
       </c>
       <c r="O105" s="13" t="inlineStr">
@@ -8892,22 +8856,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>VII</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sapientia Mediaevalis</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Carmina Burana (seleção)</t>
+          <t>Sermones, Epistulae, Ars poetica</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Anônimo (séc. XII–XIII)</t>
+          <t>Quintus Horatius Flaccus</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -8921,21 +8885,21 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>Medieval</t>
+          <t>Clássico</t>
         </is>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>Poesia lírica</t>
+          <t>Sátira</t>
         </is>
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>Vicifons (Latin Wikisource)</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -8946,7 +8910,7 @@
       <c r="M106" t="inlineStr"/>
       <c r="N106" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, EPUB, PDF</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O106" s="13" t="inlineStr">
@@ -8965,22 +8929,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>VII</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sapientia Mediaevalis</t>
+          <t>Auctores Romani</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Meditationes de prima philosophia</t>
+          <t>Saturae</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>René Descartes</t>
+          <t>Decimus Iunius Iuvenalis</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -8994,21 +8958,21 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>Renascentista e neolatino</t>
+          <t>Pós-clássico</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>Filosofia</t>
+          <t>Sátira</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>Project Gutenberg</t>
+          <t>Perseus Digital Library</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -9019,7 +8983,7 @@
       <c r="M107" t="inlineStr"/>
       <c r="N107" s="4" t="inlineStr">
         <is>
-          <t>Leitura online, EPUB, Texto</t>
+          <t>Leitura online, XML</t>
         </is>
       </c>
       <c r="O107" s="13" t="inlineStr">
@@ -9032,9 +8996,2892 @@
       <c r="R107" s="14" t="n"/>
       <c r="T107" t="inlineStr"/>
     </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Auctores Romani</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>Saturae</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Aulus Persius Flaccus</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>5</v>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>Pós-clássico</t>
+        </is>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>Sátira</t>
+        </is>
+      </c>
+      <c r="K108" s="4" t="inlineStr">
+        <is>
+          <t>Perseus Digital Library</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, XML</t>
+        </is>
+      </c>
+      <c r="O108" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" s="14" t="n"/>
+      <c r="R108" s="14" t="n"/>
+      <c r="T108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Auctores Romani</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Tragoediae (as dez tragédias)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Lucius Annaeus Seneca</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>5</v>
+      </c>
+      <c r="I109" s="4" t="inlineStr">
+        <is>
+          <t>Pós-clássico</t>
+        </is>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>Tragédia</t>
+        </is>
+      </c>
+      <c r="K109" s="4" t="inlineStr">
+        <is>
+          <t>Perseus Digital Library</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, XML</t>
+        </is>
+      </c>
+      <c r="O109" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" s="14" t="n"/>
+      <c r="R109" s="14" t="n"/>
+      <c r="T109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Auctores Romani</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>Georgica, liber IV</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Publius Vergilius Maro</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>5</v>
+      </c>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t>Clássico</t>
+        </is>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>Poesia didática</t>
+        </is>
+      </c>
+      <c r="K110" s="4" t="inlineStr">
+        <is>
+          <t>Dickinson College Commentaries</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="N110" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, Áudio</t>
+        </is>
+      </c>
+      <c r="O110" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" s="14" t="n"/>
+      <c r="R110" s="14" t="n"/>
+      <c r="T110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Auctores Romani</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>Georgica (texto integral)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Publius Vergilius Maro</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>5</v>
+      </c>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>Clássico</t>
+        </is>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>Poesia didática</t>
+        </is>
+      </c>
+      <c r="K111" s="4" t="inlineStr">
+        <is>
+          <t>Perseus Digital Library</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, XML</t>
+        </is>
+      </c>
+      <c r="O111" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" s="14" t="n"/>
+      <c r="R111" s="14" t="n"/>
+      <c r="T111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Auctores Romani</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>Apologia (Pro se de magia)</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Apuleius Madaurensis</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>5</v>
+      </c>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t>Pós-clássico</t>
+        </is>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>Oratória</t>
+        </is>
+      </c>
+      <c r="K112" s="4" t="inlineStr">
+        <is>
+          <t>Dickinson College Commentaries</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online</t>
+        </is>
+      </c>
+      <c r="O112" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" s="14" t="n"/>
+      <c r="R112" s="14" t="n"/>
+      <c r="T112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Auctores Romani</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>Metamorphoses (Asinus aureus)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Lucius Apuleius</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>5</v>
+      </c>
+      <c r="I113" s="4" t="inlineStr">
+        <is>
+          <t>Pós-clássico</t>
+        </is>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>Romance</t>
+        </is>
+      </c>
+      <c r="K113" s="4" t="inlineStr">
+        <is>
+          <t>Perseus Digital Library</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, XML</t>
+        </is>
+      </c>
+      <c r="O113" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" s="14" t="n"/>
+      <c r="R113" s="14" t="n"/>
+      <c r="T113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Auctores Romani</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>De architectura</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Marcus Vitruvius Pollio</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>4</v>
+      </c>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t>Clássico</t>
+        </is>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>Tratado técnico</t>
+        </is>
+      </c>
+      <c r="K114" s="4" t="inlineStr">
+        <is>
+          <t>Perseus Digital Library</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, XML</t>
+        </is>
+      </c>
+      <c r="O114" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" s="14" t="n"/>
+      <c r="R114" s="14" t="n"/>
+      <c r="T114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Auctores Romani</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>Mosella</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Decimus Magnus Ausonius</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>4</v>
+      </c>
+      <c r="I115" s="4" t="inlineStr">
+        <is>
+          <t>Tardio e patrístico</t>
+        </is>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>Poesia descritiva</t>
+        </is>
+      </c>
+      <c r="K115" s="4" t="inlineStr">
+        <is>
+          <t>Perseus Digital Library</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, XML</t>
+        </is>
+      </c>
+      <c r="O115" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" s="14" t="n"/>
+      <c r="R115" s="14" t="n"/>
+      <c r="T115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Latinitas Christiana</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>Biblia Sacra Vulgata (editio Clementina)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Hieronymus Stridonensis (Vulgata)</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>2</v>
+      </c>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t>Tardio e patrístico</t>
+        </is>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>Escritura (Vulgata)</t>
+        </is>
+      </c>
+      <c r="K116" s="4" t="inlineStr">
+        <is>
+          <t>Vicifons (Latin Wikisource)</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="N116" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, EPUB, PDF, Áudio</t>
+        </is>
+      </c>
+      <c r="O116" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" s="14" t="n"/>
+      <c r="R116" s="14" t="n"/>
+      <c r="T116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Latinitas Christiana</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>Prophetia Ionae (Vulgata)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Hieronymus Stridonensis (Vulgata)</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>2</v>
+      </c>
+      <c r="I117" s="4" t="inlineStr">
+        <is>
+          <t>Tardio e patrístico</t>
+        </is>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>Escritura (Vulgata)</t>
+        </is>
+      </c>
+      <c r="K117" s="4" t="inlineStr">
+        <is>
+          <t>Project Gutenberg</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, EPUB, Texto</t>
+        </is>
+      </c>
+      <c r="O117" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" s="14" t="n"/>
+      <c r="R117" s="14" t="n"/>
+      <c r="T117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Latinitas Christiana</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>Regula sancti Benedicti</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Benedictus Nursinus</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>2</v>
+      </c>
+      <c r="I118" s="4" t="inlineStr">
+        <is>
+          <t>Tardio e patrístico</t>
+        </is>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>Regra monástica</t>
+        </is>
+      </c>
+      <c r="K118" s="4" t="inlineStr">
+        <is>
+          <t>Vicifons (Latin Wikisource)</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="N118" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, EPUB, PDF, Áudio</t>
+        </is>
+      </c>
+      <c r="O118" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" s="14" t="n"/>
+      <c r="R118" s="14" t="n"/>
+      <c r="T118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Latinitas Christiana</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>Vita Sancti Martini</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Sulpicius Severus</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>3</v>
+      </c>
+      <c r="I119" s="4" t="inlineStr">
+        <is>
+          <t>Tardio e patrístico</t>
+        </is>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>Hagiografia</t>
+        </is>
+      </c>
+      <c r="K119" s="4" t="inlineStr">
+        <is>
+          <t>Dickinson College Commentaries</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="N119" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, Áudio</t>
+        </is>
+      </c>
+      <c r="O119" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" s="14" t="n"/>
+      <c r="R119" s="14" t="n"/>
+      <c r="T119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Latinitas Christiana</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>De imitatione Christi</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Thomas a Kempis</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>2</v>
+      </c>
+      <c r="I120" s="4" t="inlineStr">
+        <is>
+          <t>Medieval</t>
+        </is>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>Espiritualidade</t>
+        </is>
+      </c>
+      <c r="K120" s="4" t="inlineStr">
+        <is>
+          <t>Vicifons (Latin Wikisource)</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="N120" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, EPUB, PDF, Áudio</t>
+        </is>
+      </c>
+      <c r="O120" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" s="14" t="n"/>
+      <c r="R120" s="14" t="n"/>
+      <c r="T120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Latinitas Christiana</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>Vita Malchi monachi captivi</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Hieronymus Stridonensis</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>3</v>
+      </c>
+      <c r="I121" s="4" t="inlineStr">
+        <is>
+          <t>Tardio e patrístico</t>
+        </is>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>Hagiografia</t>
+        </is>
+      </c>
+      <c r="K121" s="4" t="inlineStr">
+        <is>
+          <t>Dickinson College Commentaries</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online</t>
+        </is>
+      </c>
+      <c r="O121" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" s="14" t="n"/>
+      <c r="R121" s="14" t="n"/>
+      <c r="T121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Latinitas Christiana</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>Vita Sancti Pauli primi eremitae</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Hieronymus Stridonensis</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>3</v>
+      </c>
+      <c r="I122" s="4" t="inlineStr">
+        <is>
+          <t>Tardio e patrístico</t>
+        </is>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>Hagiografia</t>
+        </is>
+      </c>
+      <c r="K122" s="4" t="inlineStr">
+        <is>
+          <t>Corpus Corporum</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, XML</t>
+        </is>
+      </c>
+      <c r="O122" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" s="14" t="n"/>
+      <c r="R122" s="14" t="n"/>
+      <c r="T122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Latinitas Christiana</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>Confessiones</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Augustinus Hipponensis</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>4</v>
+      </c>
+      <c r="I123" s="4" t="inlineStr">
+        <is>
+          <t>Tardio e patrístico</t>
+        </is>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>Autobiografia</t>
+        </is>
+      </c>
+      <c r="K123" s="4" t="inlineStr">
+        <is>
+          <t>Corpus Corporum</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="N123" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, XML, EPUB, Áudio</t>
+        </is>
+      </c>
+      <c r="O123" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" s="14" t="n"/>
+      <c r="R123" s="14" t="n"/>
+      <c r="T123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Latinitas Christiana</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>Epistulae (18 cartas selecionadas)</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Hieronymus Stridonensis</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>4</v>
+      </c>
+      <c r="I124" s="4" t="inlineStr">
+        <is>
+          <t>Tardio e patrístico</t>
+        </is>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>Epistolografia</t>
+        </is>
+      </c>
+      <c r="K124" s="4" t="inlineStr">
+        <is>
+          <t>Perseus Digital Library</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online</t>
+        </is>
+      </c>
+      <c r="O124" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" s="14" t="n"/>
+      <c r="R124" s="14" t="n"/>
+      <c r="T124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Latinitas Christiana</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>Epistolae (texto integral)</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Hieronymus Stridonensis</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>4</v>
+      </c>
+      <c r="I125" s="4" t="inlineStr">
+        <is>
+          <t>Tardio e patrístico</t>
+        </is>
+      </c>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t>Epistolografia</t>
+        </is>
+      </c>
+      <c r="K125" s="4" t="inlineStr">
+        <is>
+          <t>Corpus Corporum</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, XML</t>
+        </is>
+      </c>
+      <c r="O125" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" s="14" t="n"/>
+      <c r="R125" s="14" t="n"/>
+      <c r="T125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Latinitas Christiana</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>Epistulae (cartas selecionadas)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Augustinus Hipponensis</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>4</v>
+      </c>
+      <c r="I126" s="4" t="inlineStr">
+        <is>
+          <t>Tardio e patrístico</t>
+        </is>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>Epistolografia</t>
+        </is>
+      </c>
+      <c r="K126" s="4" t="inlineStr">
+        <is>
+          <t>Perseus Digital Library</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online</t>
+        </is>
+      </c>
+      <c r="O126" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" s="14" t="n"/>
+      <c r="R126" s="14" t="n"/>
+      <c r="T126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Latinitas Christiana</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>De civitate Dei</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Augustinus Hipponensis</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>4</v>
+      </c>
+      <c r="I127" s="4" t="inlineStr">
+        <is>
+          <t>Tardio e patrístico</t>
+        </is>
+      </c>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t>Teologia</t>
+        </is>
+      </c>
+      <c r="K127" s="4" t="inlineStr">
+        <is>
+          <t>Corpus Corporum</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="N127" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, XML, Áudio</t>
+        </is>
+      </c>
+      <c r="O127" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" s="14" t="n"/>
+      <c r="R127" s="14" t="n"/>
+      <c r="T127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Latinitas Christiana</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>Te Deum</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Atribuído a Nicetas de Remesiana ou a Ambrósio</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>2</v>
+      </c>
+      <c r="I128" s="4" t="inlineStr">
+        <is>
+          <t>Tardio e patrístico</t>
+        </is>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>Hino</t>
+        </is>
+      </c>
+      <c r="K128" s="4" t="inlineStr">
+        <is>
+          <t>Vicifons (Latin Wikisource)</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, EPUB, PDF</t>
+        </is>
+      </c>
+      <c r="O128" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" s="14" t="n"/>
+      <c r="R128" s="14" t="n"/>
+      <c r="T128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Latinitas Christiana</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>Pange lingua gloriosi corporis mysterium</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Thomas de Aquino</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>3</v>
+      </c>
+      <c r="I129" s="4" t="inlineStr">
+        <is>
+          <t>Medieval</t>
+        </is>
+      </c>
+      <c r="J129" s="4" t="inlineStr">
+        <is>
+          <t>Hino</t>
+        </is>
+      </c>
+      <c r="K129" s="4" t="inlineStr">
+        <is>
+          <t>Vicifons (Latin Wikisource)</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, EPUB, PDF</t>
+        </is>
+      </c>
+      <c r="O129" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" s="14" t="n"/>
+      <c r="R129" s="14" t="n"/>
+      <c r="T129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Latinitas Christiana</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>Dies irae</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Atribuído a Thomas de Celano</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>3</v>
+      </c>
+      <c r="I130" s="4" t="inlineStr">
+        <is>
+          <t>Medieval</t>
+        </is>
+      </c>
+      <c r="J130" s="4" t="inlineStr">
+        <is>
+          <t>Hino</t>
+        </is>
+      </c>
+      <c r="K130" s="4" t="inlineStr">
+        <is>
+          <t>Vicifons (Latin Wikisource)</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, EPUB, PDF</t>
+        </is>
+      </c>
+      <c r="O130" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" s="14" t="n"/>
+      <c r="R130" s="14" t="n"/>
+      <c r="T130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Latinitas Christiana</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>Stabat Mater</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Atribuído a Jacopone da Todi</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>2</v>
+      </c>
+      <c r="I131" s="4" t="inlineStr">
+        <is>
+          <t>Medieval</t>
+        </is>
+      </c>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t>Hino</t>
+        </is>
+      </c>
+      <c r="K131" s="4" t="inlineStr">
+        <is>
+          <t>Vicifons (Latin Wikisource)</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="N131" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, EPUB, PDF, Áudio</t>
+        </is>
+      </c>
+      <c r="O131" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" s="14" t="n"/>
+      <c r="R131" s="14" t="n"/>
+      <c r="T131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Sapientia Mediaevalis</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>Navigatio Sancti Brendani Abbatis</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Anônimo (séc. IX–X)</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>2</v>
+      </c>
+      <c r="I132" s="4" t="inlineStr">
+        <is>
+          <t>Medieval</t>
+        </is>
+      </c>
+      <c r="J132" s="4" t="inlineStr">
+        <is>
+          <t>Narrativa</t>
+        </is>
+      </c>
+      <c r="K132" s="4" t="inlineStr">
+        <is>
+          <t>Dickinson College Commentaries</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online</t>
+        </is>
+      </c>
+      <c r="O132" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" s="14" t="n"/>
+      <c r="R132" s="14" t="n"/>
+      <c r="T132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Sapientia Mediaevalis</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>Gesta Romanorum (edição Oesterley)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Anônimo (séc. XIII–XIV)</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>2</v>
+      </c>
+      <c r="I133" s="4" t="inlineStr">
+        <is>
+          <t>Medieval</t>
+        </is>
+      </c>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>Narrativa</t>
+        </is>
+      </c>
+      <c r="K133" s="4" t="inlineStr">
+        <is>
+          <t>Vicifons (Latin Wikisource)</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, EPUB, PDF</t>
+        </is>
+      </c>
+      <c r="O133" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" s="14" t="n"/>
+      <c r="R133" s="14" t="n"/>
+      <c r="T133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Sapientia Mediaevalis</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>De consolatione philosophiae</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Anicius Manlius Severinus Boethius</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>4</v>
+      </c>
+      <c r="I134" s="4" t="inlineStr">
+        <is>
+          <t>Tardio e patrístico</t>
+        </is>
+      </c>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t>Filosofia</t>
+        </is>
+      </c>
+      <c r="K134" s="4" t="inlineStr">
+        <is>
+          <t>Corpus Corporum</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="N134" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, XML, EPUB, Áudio</t>
+        </is>
+      </c>
+      <c r="O134" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" s="14" t="n"/>
+      <c r="R134" s="14" t="n"/>
+      <c r="T134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Sapientia Mediaevalis</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>Historia Ecclesiastica gentis Anglorum (seleções)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Beda Venerabilis</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>3</v>
+      </c>
+      <c r="I135" s="4" t="inlineStr">
+        <is>
+          <t>Medieval</t>
+        </is>
+      </c>
+      <c r="J135" s="4" t="inlineStr">
+        <is>
+          <t>Historiografia</t>
+        </is>
+      </c>
+      <c r="K135" s="4" t="inlineStr">
+        <is>
+          <t>Dickinson College Commentaries</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online</t>
+        </is>
+      </c>
+      <c r="O135" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" s="14" t="n"/>
+      <c r="R135" s="14" t="n"/>
+      <c r="T135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Sapientia Mediaevalis</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>Vita Karoli Magni</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Einhardus</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>3</v>
+      </c>
+      <c r="I136" s="4" t="inlineStr">
+        <is>
+          <t>Medieval</t>
+        </is>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>Biografia</t>
+        </is>
+      </c>
+      <c r="K136" s="4" t="inlineStr">
+        <is>
+          <t>Vicifons (Latin Wikisource)</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, EPUB, PDF</t>
+        </is>
+      </c>
+      <c r="O136" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" s="14" t="n"/>
+      <c r="R136" s="14" t="n"/>
+      <c r="T136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Sapientia Mediaevalis</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>Gesta Francorum et aliorum Hierosolimitanorum</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Anônimo (c. 1100)</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>3</v>
+      </c>
+      <c r="I137" s="4" t="inlineStr">
+        <is>
+          <t>Medieval</t>
+        </is>
+      </c>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
+          <t>Historiografia</t>
+        </is>
+      </c>
+      <c r="K137" s="4" t="inlineStr">
+        <is>
+          <t>Dickinson College Commentaries</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online</t>
+        </is>
+      </c>
+      <c r="O137" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" s="14" t="n"/>
+      <c r="R137" s="14" t="n"/>
+      <c r="T137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Sapientia Mediaevalis</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>Legenda aurea (capítulos transcritos)</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Iacobus de Voragine</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>3</v>
+      </c>
+      <c r="I138" s="4" t="inlineStr">
+        <is>
+          <t>Medieval</t>
+        </is>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>Hagiografia</t>
+        </is>
+      </c>
+      <c r="K138" s="4" t="inlineStr">
+        <is>
+          <t>Vicifons (Latin Wikisource)</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, EPUB, PDF</t>
+        </is>
+      </c>
+      <c r="O138" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" s="14" t="n"/>
+      <c r="R138" s="14" t="n"/>
+      <c r="T138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Sapientia Mediaevalis</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>Proslogion</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Anselmus Cantuariensis</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>3</v>
+      </c>
+      <c r="I139" s="4" t="inlineStr">
+        <is>
+          <t>Medieval</t>
+        </is>
+      </c>
+      <c r="J139" s="4" t="inlineStr">
+        <is>
+          <t>Filosofia</t>
+        </is>
+      </c>
+      <c r="K139" s="4" t="inlineStr">
+        <is>
+          <t>Corpus Corporum</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, XML</t>
+        </is>
+      </c>
+      <c r="O139" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" s="14" t="n"/>
+      <c r="R139" s="14" t="n"/>
+      <c r="T139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Sapientia Mediaevalis</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>Etymologiae</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Isidorus Hispalensis</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>3</v>
+      </c>
+      <c r="I140" s="4" t="inlineStr">
+        <is>
+          <t>Medieval</t>
+        </is>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>Enciclopédia</t>
+        </is>
+      </c>
+      <c r="K140" s="4" t="inlineStr">
+        <is>
+          <t>Corpus Corporum</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, XML</t>
+        </is>
+      </c>
+      <c r="O140" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" s="14" t="n"/>
+      <c r="R140" s="14" t="n"/>
+      <c r="T140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Sapientia Mediaevalis</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>De diligendo Deo</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Bernardus Claraevallensis</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>3</v>
+      </c>
+      <c r="I141" s="4" t="inlineStr">
+        <is>
+          <t>Medieval</t>
+        </is>
+      </c>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t>Teologia</t>
+        </is>
+      </c>
+      <c r="K141" s="4" t="inlineStr">
+        <is>
+          <t>Corpus Corporum</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, XML</t>
+        </is>
+      </c>
+      <c r="O141" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr"/>
+      <c r="Q141" s="14" t="n"/>
+      <c r="R141" s="14" t="n"/>
+      <c r="T141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Sapientia Mediaevalis</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>Didascalicon (Eruditio didascalica)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Hugo de Sancto Victore</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>3</v>
+      </c>
+      <c r="I142" s="4" t="inlineStr">
+        <is>
+          <t>Medieval</t>
+        </is>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t>Filosofia</t>
+        </is>
+      </c>
+      <c r="K142" s="4" t="inlineStr">
+        <is>
+          <t>Corpus Corporum</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, XML</t>
+        </is>
+      </c>
+      <c r="O142" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" s="14" t="n"/>
+      <c r="R142" s="14" t="n"/>
+      <c r="T142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Sapientia Mediaevalis</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>Summa Theologiae, Prima pars</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Thomas de Aquino</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>3</v>
+      </c>
+      <c r="I143" s="4" t="inlineStr">
+        <is>
+          <t>Medieval</t>
+        </is>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>Teologia</t>
+        </is>
+      </c>
+      <c r="K143" s="4" t="inlineStr">
+        <is>
+          <t>Corpus Thomisticum</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online</t>
+        </is>
+      </c>
+      <c r="O143" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr"/>
+      <c r="Q143" s="14" t="n"/>
+      <c r="R143" s="14" t="n"/>
+      <c r="T143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Sapientia Mediaevalis</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>De ente et essentia</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Thomas de Aquino</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>4</v>
+      </c>
+      <c r="I144" s="4" t="inlineStr">
+        <is>
+          <t>Medieval</t>
+        </is>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>Filosofia</t>
+        </is>
+      </c>
+      <c r="K144" s="4" t="inlineStr">
+        <is>
+          <t>Corpus Thomisticum</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online</t>
+        </is>
+      </c>
+      <c r="O144" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr"/>
+      <c r="Q144" s="14" t="n"/>
+      <c r="R144" s="14" t="n"/>
+      <c r="T144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Sapientia Mediaevalis</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>Carmina Burana (seleção)</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Anônimo (séc. XII–XIII)</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>4</v>
+      </c>
+      <c r="I145" s="4" t="inlineStr">
+        <is>
+          <t>Medieval</t>
+        </is>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>Poesia lírica</t>
+        </is>
+      </c>
+      <c r="K145" s="4" t="inlineStr">
+        <is>
+          <t>Vicifons (Latin Wikisource)</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, EPUB, PDF</t>
+        </is>
+      </c>
+      <c r="O145" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" s="14" t="n"/>
+      <c r="R145" s="14" t="n"/>
+      <c r="T145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Sapientia Mediaevalis</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>Meditationes de prima philosophia</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>René Descartes</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>4</v>
+      </c>
+      <c r="I146" s="4" t="inlineStr">
+        <is>
+          <t>Renascentista e neolatino</t>
+        </is>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>Filosofia</t>
+        </is>
+      </c>
+      <c r="K146" s="4" t="inlineStr">
+        <is>
+          <t>Project Gutenberg</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" s="4" t="inlineStr">
+        <is>
+          <t>Leitura online, EPUB, Texto</t>
+        </is>
+      </c>
+      <c r="O146" s="13" t="inlineStr">
+        <is>
+          <t>abrir ↗</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" s="14" t="n"/>
+      <c r="R146" s="14" t="n"/>
+      <c r="T146" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T107"/>
-  <conditionalFormatting sqref="P2:P107">
+  <autoFilter ref="A1:T146"/>
+  <conditionalFormatting sqref="P2:P146">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Lido"</formula>
     </cfRule>
@@ -9046,10 +11893,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="P2:P107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Quero ler,Lendo,Lido,Abandonei"</formula1>
     </dataValidation>
-    <dataValidation sqref="S2:S107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="S2:S146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
@@ -9161,6 +12008,45 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O105" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="rId105"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O146" r:id="rId145"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
